--- a/从零开始学Slots/从零开始学Slots-41-数值篇-RandomWild.xlsx
+++ b/从零开始学Slots/从零开始学Slots-41-数值篇-RandomWild.xlsx
@@ -8470,6 +8470,9 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <ignoredErrors>
+    <ignoredError sqref="A1:M152" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
@@ -9351,5 +9354,8 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <ignoredErrors>
+    <ignoredError sqref="A1:S81" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
--- a/从零开始学Slots/从零开始学Slots-41-数值篇-RandomWild.xlsx
+++ b/从零开始学Slots/从零开始学Slots-41-数值篇-RandomWild.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="197">
   <si>
     <r>
       <rPr>
@@ -7413,7 +7413,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="37">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -7548,6 +7548,18 @@
     </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -8129,13 +8141,13 @@
       </c>
     </row>
     <row r="65" customFormat="false" ht="16" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="5" t="s">
-        <v>52</v>
+      <c r="A65" s="34">
+        <v>6</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="16" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="5" t="s">
-        <v>53</v>
+      <c r="A66" s="34">
+        <v>1</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="16" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8573,8 +8585,8 @@
         <f aca="false">2^5</f>
         <v>32</v>
       </c>
-      <c r="C8" s="19" t="s">
-        <v>119</v>
+      <c r="C8" s="35">
+        <v>5</v>
       </c>
       <c r="D8" s="19"/>
       <c r="E8" s="19"/>
@@ -8660,8 +8672,8 @@
       <c r="B15" s="18" t="s">
         <v>129</v>
       </c>
-      <c r="C15" s="19" t="s">
-        <v>130</v>
+      <c r="C15" s="35">
+        <v>5</v>
       </c>
       <c r="D15" s="19"/>
       <c r="E15" s="19"/>
@@ -9243,8 +9255,8 @@
       <c r="H54" s="14"/>
     </row>
     <row r="55" customFormat="false" ht="16" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="16" t="s">
-        <v>187</v>
+      <c r="A55" s="36">
+        <v>8</v>
       </c>
       <c r="B55" s="28" t="str">
         <f aca="false">IF(COUNTA($A$23:$A$30)=8,"✓","✗")</f>

--- a/从零开始学Slots/从零开始学Slots-41-数值篇-RandomWild.xlsx
+++ b/从零开始学Slots/从零开始学Slots-41-数值篇-RandomWild.xlsx
@@ -7230,12 +7230,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0"/>
     <numFmt numFmtId="166" formatCode="0.0000%"/>
     <numFmt numFmtId="167" formatCode="0.0000"/>
     <numFmt numFmtId="168" formatCode="0.00%"/>
+    <numFmt numFmtId="169" formatCode="0.0000000000%"/>
   </numFmts>
   <fonts count="17">
     <font>
@@ -7413,7 +7414,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="39">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -7559,6 +7560,14 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" applyNumberFormat="1" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" applyNumberFormat="1" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -8785,7 +8794,7 @@
         <f aca="false">IF($B$22&lt;E23,0,COMBIN(6,$B$22-E23))</f>
         <v>20</v>
       </c>
-      <c r="G23" s="22" t="n">
+      <c r="G23" s="37" t="n">
         <f aca="false">F23/COMBIN(9,$B$22)</f>
         <v>0.238095238095238</v>
       </c>
@@ -8811,7 +8820,7 @@
         <f aca="false">IF($B$22&lt;E24,0,COMBIN(6,$B$22-E24))</f>
         <v>15</v>
       </c>
-      <c r="G24" s="22" t="n">
+      <c r="G24" s="37" t="n">
         <f aca="false">F24/COMBIN(9,$B$22)</f>
         <v>0.178571428571429</v>
       </c>
@@ -8837,7 +8846,7 @@
         <f aca="false">IF($B$22&lt;E25,0,COMBIN(6,$B$22-E25))</f>
         <v>15</v>
       </c>
-      <c r="G25" s="22" t="n">
+      <c r="G25" s="37" t="n">
         <f aca="false">F25/COMBIN(9,$B$22)</f>
         <v>0.178571428571429</v>
       </c>
@@ -8863,7 +8872,7 @@
         <f aca="false">IF($B$22&lt;E26,0,COMBIN(6,$B$22-E26))</f>
         <v>15</v>
       </c>
-      <c r="G26" s="22" t="n">
+      <c r="G26" s="37" t="n">
         <f aca="false">F26/COMBIN(9,$B$22)</f>
         <v>0.178571428571429</v>
       </c>
@@ -8889,7 +8898,7 @@
         <f aca="false">IF($B$22&lt;E27,0,COMBIN(6,$B$22-E27))</f>
         <v>6</v>
       </c>
-      <c r="G27" s="22" t="n">
+      <c r="G27" s="37" t="n">
         <f aca="false">F27/COMBIN(9,$B$22)</f>
         <v>0.0714285714285714</v>
       </c>
@@ -8915,7 +8924,7 @@
         <f aca="false">IF($B$22&lt;E28,0,COMBIN(6,$B$22-E28))</f>
         <v>6</v>
       </c>
-      <c r="G28" s="22" t="n">
+      <c r="G28" s="37" t="n">
         <f aca="false">F28/COMBIN(9,$B$22)</f>
         <v>0.0714285714285714</v>
       </c>
@@ -8941,7 +8950,7 @@
         <f aca="false">IF($B$22&lt;E29,0,COMBIN(6,$B$22-E29))</f>
         <v>6</v>
       </c>
-      <c r="G29" s="22" t="n">
+      <c r="G29" s="37" t="n">
         <f aca="false">F29/COMBIN(9,$B$22)</f>
         <v>0.0714285714285714</v>
       </c>
@@ -8967,7 +8976,7 @@
         <f aca="false">IF($B$22&lt;E30,0,COMBIN(6,$B$22-E30))</f>
         <v>1</v>
       </c>
-      <c r="G30" s="22" t="n">
+      <c r="G30" s="37" t="n">
         <f aca="false">F30/COMBIN(9,$B$22)</f>
         <v>0.0119047619047619</v>
       </c>
@@ -8983,7 +8992,7 @@
         <f aca="false">SUM(F23:F30)</f>
         <v>84</v>
       </c>
-      <c r="G31" s="22" t="n">
+      <c r="G31" s="37" t="n">
         <f aca="false">SUM(G23:G30)</f>
         <v>1</v>
       </c>
